--- a/data/logs/ean-problems/logs.xlsx
+++ b/data/logs/ean-problems/logs.xlsx
@@ -6,7 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="logs" r:id="rId5" sheetId="15"/>
+    <sheet name="New Stock" r:id="rId3" sheetId="1"/>
+    <sheet name="logs" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -53,9 +54,182 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="0">
+        <is>
+          <t>ean</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="0">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="0">
+        <is>
+          <t>allergens</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="0">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="0">
+        <is>
+          <t>image_front_url</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="0">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="0">
+        <is>
+          <t>expirationdate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="0">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="0">
+        <is>
+          <t>5601049132995</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t>leite</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="0">
+        <is>
+          <t>Leites meio gordo, Leites UHT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t>https://images.openfoodfacts.org/images/products/560/104/913/2995/front_pt.85.400.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="0">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="0">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="0">
+        <is>
+          <t>5601049132995</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="0">
+        <is>
+          <t>leite</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="0">
+        <is>
+          <t>Leites meio gordo, Leites UHT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="0">
+        <is>
+          <t>https://images.openfoodfacts.org/images/products/560/104/913/2995/front_pt.85.400.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="0">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="0">
+        <is>
+          <t>27/03/2027</t>
+        </is>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="0">
+        <is>
+          <t>8410500028794</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="0">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="0">
+        <is>
+          <t>leche</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="0">
+        <is>
+          <t>Yogures estilo griego, Yogures naturales</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="0">
+        <is>
+          <t>https://images.openfoodfacts.org/images/products/841/050/002/8794/front_es.35.400.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="0">
+        <is>
+          <t>Griego natural</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="0">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -82,56 +256,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>failure_reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2000000000010</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>05/01/2028</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>API Enrichment (Join)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EAN not found in API</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>56010491329</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>27/03/2027</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EAN Validation</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EAN-13 format</t>
         </is>
       </c>
     </row>

--- a/data/logs/ean-problems/logs.xlsx
+++ b/data/logs/ean-problems/logs.xlsx
@@ -56,7 +56,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -181,46 +181,6 @@
         <v>120.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr" s="0">
-        <is>
-          <t>8410500028794</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="0">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="0">
-        <is>
-          <t>leche</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="0">
-        <is>
-          <t>Yogures estilo griego, Yogures naturales</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="0">
-        <is>
-          <t>https://images.openfoodfacts.org/images/products/841/050/002/8794/front_es.35.400.jpg</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="0">
-        <is>
-          <t>Griego natural</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr" s="0">
-        <is>
-          <t>29/10/2026</t>
-        </is>
-      </c>
-      <c r="H4" t="n" s="0">
-        <v>4.0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -229,7 +189,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -240,22 +200,29 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>expirationdate</t>
+          <t>pipeline_stage</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pipeline_stage</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>failure_reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8410500028794</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Product Matching</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EAN not found in CSV</t>
         </is>
       </c>
     </row>
